--- a/Data/prompts.xlsx
+++ b/Data/prompts.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trending Prompts" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Shelf" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -93,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -110,6 +111,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -710,7 +712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -782,6 +784,251 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ABOUT THE 'PROMPT SHELF' TAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>This tab feeds the 'Copy the prompt. Paste it in. Done.' section on the site — every row here shows up (no Trending flag needed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Same columns as the Trending tab, minus 'Trending (Yes/No)'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Order controls left-to-right / top-to-bottom position.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Image Filename works the same way — must match a file in /Images exactly, or leave blank for a color card.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Prompt Text</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Image Filename</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Bardot Studio Portrait</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Studio</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>soft light · editorial</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Edit this photo into a studio portrait with soft off-shoulder top, warm diffused key light from the left, neutral backdrop, shallow depth of field, natural skin texture, ultra-realistic RAW finish.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Campus Golden Hour</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Campus</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>candid · daylight</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Place the subject on a sunlit college pathway, autumn tones, candid walking pose, backpack over one shoulder, warm golden-hour light, cinematic color grade, natural motion blur in background.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Coastal Cinematic</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Beach</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>beach · long shadow</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Reimagine the scene on a quiet beach at golden hour, flowing fabric caught mid-breeze, long soft shadows, warm film-grain grade, wide cinematic aspect ratio, gentle lens flare.</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Kurti Street Edit</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Street</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>everyday · natural light</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Style the subject in a printed kurti with straight denim, relaxed street pose against a textured wall, soft overcast daylight, true-to-life color balance, subtle editorial vignette.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Sharara Palace Hour</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Festival</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>festival · royal light</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Transform the outfit into a detailed sharara set, set against a warmly lit palace archway, rich jewel tones, elegant standing pose, soft rim light, editorial fashion-shoot finish.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Quiet Luxury Frame</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>lifestyle · muted tone</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Recompose as a quiet-luxury lifestyle photo, muted neutral palette, clean studio or hotel-lobby backdrop, relaxed confident posture, soft top-down light, minimal color grade.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
